--- a/doc/zh_CN.xlsx
+++ b/doc/zh_CN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\QT\workSpace\BMSTOOL\bmsTool\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{31D6604C-F803-45D9-9AEA-0E22148713B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{C590AC8D-21A2-4BB9-8ABC-872B357DDDD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7C963E8C-04BA-4540-A8FA-3FA84A5BCB13}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="23250" windowHeight="12810" xr2:uid="{A4AFF391-0089-4868-A7D4-45C07B78E8B0}"/>
   </bookViews>
   <sheets>
     <sheet name="zh_CN" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="243">
   <si>
     <t>单体电池低压告警</t>
   </si>
@@ -136,7 +136,7 @@
     <t>模块温度,I16,0.1,0,℃</t>
   </si>
   <si>
-    <t>模块温度复归</t>
+    <t>模块温度故障复归</t>
   </si>
   <si>
     <t>模块温度ID,U16,1,0,</t>
@@ -172,7 +172,7 @@
     <t>过流故障</t>
   </si>
   <si>
-    <t>过流复归</t>
+    <t>过流故障复归</t>
   </si>
   <si>
     <t>短路故障</t>
@@ -355,7 +355,7 @@
     <t>温度断线状态字,U16,1,0,</t>
   </si>
   <si>
-    <t>簇极柱复归</t>
+    <t>簇极柱故障复归</t>
   </si>
   <si>
     <t>模块最小/最大温度,U16,1,0,℃</t>
@@ -526,6 +526,9 @@
     <t>更改后的值,U16,1,0,</t>
   </si>
   <si>
+    <t>{"evt_id":{"5358":"预充结束时间定值","5359":"预充结束电流定值","5360":"预留传感器量程","5361":"簇电池额定Ah数","5362":"充放电电流死区阈值","5363":"簇电池充满回差值","5364":"簇电池放空回差值","5365":"环控温度回差值","5366":"环控温度上限值","5367":"环控温度下限值","5368":"簇电池SOC上限告警值","5369":"簇电池SOC下限值","5370":"簇极柱温度过高告警值","5371":"簇极柱温度过高保护值","5372":"簇电池绝缘电阻告警值","5373":"簇电池漏电流告警值","5374":"单体压差过高告警值","5375":"单体压差过高保护值","5376":"单体电压过高告警值","5377":"单体电压过高保护值","5378":"单体电压过低告警值","5379":"单体电压过低保护值","5380":"单体温度过高告警值","5381":"单体温度过高保护值","5382":"单体温度过低告警值","5383":"单体温度过低保护值","5384":"单体温差过高告警值","5385":"单体温差过高保护值","5386":"单体温升过高告警值","5387":"单体温升过高保护值","5388":"Pack极柱温度过高告警值","5389":"Pack极柱温度过高保护值","5390":"充放电电流过负荷告警值","5391":"充放电电流过负荷保护值","5392":"短路电流保护值","5393":"簇电压过高告警值","5394":"簇电压过高保护值","5395":"簇电压过低告警值","5396":"簇电压过低保护值","5397":"簇电池绝缘电阻保护值","5398":"簇电池漏电流保护值","5399":"告警延时","5400":"保护延时","5401":"簇电池容量","5402":"簇电池校正容量","5403":"簇电池剩余电量","5404":"充放电额定电流","5405":"电流传感器量程","5406":"漏电流传感器量程","5407":"电压传感器量程","5408":"电池均衡控制模式","5409":"均衡配置参数/阈值","5410":"均衡启动电压差值","5411":"簇电池单元数量","5412":"BMU单体电池个数","5413":"BMU模块温度个数","5414":"BMU极柱温度个数","5415":"nBC报警屏蔽位","5416":"nBC故障屏蔽位","5417":"CMU功能使能位1","5418":"IP地址低位","5419":"IP地址高位 ","5420":"NTP服务器地址低位","5421":"NTP服务器地址高位","5422":"数据屏蔽位1","5423":"数据屏蔽位2","5424":"数据屏蔽位3","5425":"数据屏蔽位4","5426":"系统保护屏蔽寄存器1","5427":"系统保护屏蔽寄存器2","5428":"系统告警屏蔽寄存器1","5429":"系统告警屏蔽寄存器2","5430":"CMU功能使能位2","5431":"充满放空簇电压回差值","5432":"单体电压数据屏蔽位","5433":"温度数据屏蔽位"}}</t>
+  </si>
+  <si>
     <t>CMU升级档校验失败</t>
   </si>
   <si>
@@ -574,9 +577,6 @@
     <t>预充电流定值,I16,0.1,0,A</t>
   </si>
   <si>
-    <t>簇极柱故障复归</t>
-  </si>
-  <si>
     <t>预留</t>
   </si>
   <si>
@@ -749,10 +749,6 @@
   </si>
   <si>
     <t>跳变后温度值,U16,0.1,0,℃</t>
-  </si>
-  <si>
-    <t>{"evt_id":{"5358":"预充结束时间定值","5359":"预充结束电流定值","5360":"预留传感器量程","5361":"簇电池额定Ah数","5362":"充放电电流死区阈值","5363":"簇电池充满回差值","5364":"簇电池放空回差值","5365":"环控温度回差值","5366":"环控温度上限值","5367":"环控温度下限值","5368":"簇电池SOC上限告警值","5369":"簇电池SOC下限值","5370":"簇极柱温度过高告警值","5371":"簇极柱温度过高保护值","5372":"簇电池绝缘电阻告警值","5373":"簇电池漏电流告警值","5374":"单体压差过高告警值","5375":"单体压差过高保护值","5376":"单体电压过高告警值","5377":"单体电压过高保护值","5378":"单体电压过低告警值","5379":"单体电压过低保护值","5380":"单体温度过高告警值","5381":"单体温度过高保护值","5382":"单体温度过低告警值","5383":"单体温度过低保护值","5384":"单体温差过高告警值","5385":"单体温差过高保护值","5386":"单体温升过高告警值","5387":"单体温升过高保护值","5388":"Pack极柱温度过高告警值","5389":"Pack极柱温度过高保护值","5390":"充放电电流过负荷告警值","5391":"充放电电流过负荷保护值","5392":"短路电流保护值","5393":"簇电压过高告警值","5394":"簇电压过高保护值","5395":"簇电压过低告警值","5396":"簇电压过低保护值","5397":"簇电池绝缘电阻保护值","5398":"簇电池漏电流保护值","5399":"告警延时","5400":"保护延时","5401":"簇电池容量","5402":"簇电池校正容量","5403":"簇电池剩余电量","5404":"充放电额定电流","5405":"电流传感器量程","5406":"漏电流传感器量程","5407":"电压传感器量程","5408":"电池均衡控制模式","5409":"均衡配置参数/阈值","5410":"均衡启动电压差值","5411":"簇电池单元数量","5412":"BMU单体电池个数","5413":"BMU模块温度个数","5414":"BMU极柱温度个数","5415":"nBC报警屏蔽位","5416":"nBC故障屏蔽位","5417":"CMU功能使能位1","5418":"IP地址低位","5419":"IP地址高位 ","5420":"NTP服务器地址低位","5421":"NTP服务器地址高位","5422":"数据屏蔽位1","5423":"数据屏蔽位2","5424":"数据屏蔽位3","5425":"数据屏蔽位4","5426":"系统保护屏蔽寄存器1","5427":"系统保护屏蔽寄存器2","5428":"系统告警屏蔽寄存器1","5429":"系统告警屏蔽寄存器2","5430":"CMU功能使能位2","5431":"充满放空簇电压回差值","5432":"单体电压数据屏蔽位","5433":"温度数据屏蔽位"}}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1703,9 +1699,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E70ACA0-A5B5-4822-88EB-F06E7093CCDD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EF161D0-7657-4F31-BFFA-87BE4C3ACFFD}">
   <dimension ref="A1:H259"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="2.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="28.125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1">
@@ -4091,7 +4094,7 @@
         <v>167</v>
       </c>
       <c r="H124" t="s">
-        <v>243</v>
+        <v>168</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
@@ -4105,7 +4108,7 @@
         <v>52</v>
       </c>
       <c r="D125" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
@@ -4133,7 +4136,7 @@
         <v>54</v>
       </c>
       <c r="D127" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
@@ -4147,13 +4150,13 @@
         <v>55</v>
       </c>
       <c r="D128" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E128" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G128" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
@@ -4167,19 +4170,19 @@
         <v>56</v>
       </c>
       <c r="D129" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E129" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F129" t="s">
+        <v>176</v>
+      </c>
+      <c r="G129" t="s">
         <v>175</v>
       </c>
-      <c r="G129" t="s">
-        <v>174</v>
-      </c>
       <c r="H129" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
@@ -4193,7 +4196,7 @@
         <v>57</v>
       </c>
       <c r="D130" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
@@ -4207,7 +4210,7 @@
         <v>58</v>
       </c>
       <c r="D131" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.2">
@@ -4221,10 +4224,10 @@
         <v>59</v>
       </c>
       <c r="D132" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E132" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.2">
@@ -4238,13 +4241,13 @@
         <v>60</v>
       </c>
       <c r="D133" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F133" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G133" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.2">
@@ -4261,7 +4264,7 @@
         <v>104</v>
       </c>
       <c r="E134" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.2">
@@ -4278,7 +4281,7 @@
         <v>105</v>
       </c>
       <c r="E135" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.2">
@@ -4355,7 +4358,7 @@
         <v>66</v>
       </c>
       <c r="D139" t="s">
-        <v>184</v>
+        <v>111</v>
       </c>
       <c r="F139" t="s">
         <v>42</v>
@@ -5947,7 +5950,7 @@
         <v>52</v>
       </c>
       <c r="D218" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.2">
@@ -5975,7 +5978,7 @@
         <v>54</v>
       </c>
       <c r="D220" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.2">
@@ -5989,13 +5992,13 @@
         <v>55</v>
       </c>
       <c r="D221" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E221" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G221" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.2">
@@ -6009,19 +6012,19 @@
         <v>56</v>
       </c>
       <c r="D222" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E222" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F222" t="s">
+        <v>176</v>
+      </c>
+      <c r="G222" t="s">
         <v>175</v>
       </c>
-      <c r="G222" t="s">
-        <v>174</v>
-      </c>
       <c r="H222" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.2">
@@ -6035,7 +6038,7 @@
         <v>57</v>
       </c>
       <c r="D223" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.2">
@@ -6049,7 +6052,7 @@
         <v>58</v>
       </c>
       <c r="D224" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.2">
@@ -6063,10 +6066,10 @@
         <v>59</v>
       </c>
       <c r="D225" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E225" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.2">
@@ -6080,13 +6083,13 @@
         <v>60</v>
       </c>
       <c r="D226" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F226" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G226" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.2">
@@ -6103,7 +6106,7 @@
         <v>104</v>
       </c>
       <c r="E227" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.2">
@@ -6120,7 +6123,7 @@
         <v>105</v>
       </c>
       <c r="E228" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.2">
@@ -6197,7 +6200,7 @@
         <v>66</v>
       </c>
       <c r="D232" t="s">
-        <v>184</v>
+        <v>111</v>
       </c>
       <c r="F232" t="s">
         <v>42</v>
